--- a/static/data/exports/Retro_CG_GE_2024.xlsx
+++ b/static/data/exports/Retro_CG_GE_2024.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_CG_GE_2024.xlsx
+++ b/static/data/exports/Retro_CG_GE_2024.xlsx
@@ -576,6 +576,19 @@
           <t>INC</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>58</v>
+      </c>
       <c r="Q2" t="b">
         <v>0</v>
       </c>
@@ -638,6 +651,19 @@
           <t>BJP</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>60</v>
+      </c>
       <c r="Q3" t="b">
         <v>1</v>
       </c>
@@ -700,6 +726,19 @@
           <t>BSP</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>35</v>
+      </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
@@ -824,6 +863,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>57</v>
+      </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
@@ -886,6 +938,19 @@
           <t>AKBRPRVP</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>37</v>
+      </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
@@ -948,6 +1013,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>41</v>
+      </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
@@ -1010,6 +1088,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>50</v>
+      </c>
       <c r="Q9" t="b">
         <v>0</v>
       </c>
@@ -1072,6 +1163,19 @@
           <t>HRJSP</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>63</v>
+      </c>
       <c r="Q10" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1238,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>40</v>
+      </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
@@ -1196,6 +1313,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>49</v>
+      </c>
       <c r="Q12" t="b">
         <v>0</v>
       </c>
@@ -1258,6 +1388,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>65</v>
+      </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
@@ -1320,6 +1463,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>46</v>
+      </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
@@ -1382,6 +1538,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>39</v>
+      </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
@@ -1444,6 +1613,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>47</v>
+      </c>
       <c r="Q16" t="b">
         <v>0</v>
       </c>
@@ -1506,6 +1688,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>46</v>
+      </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
@@ -1568,6 +1763,19 @@
           <t>SaSP</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>FEMALE</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>54</v>
+      </c>
       <c r="Q18" t="b">
         <v>0</v>
       </c>
@@ -1630,6 +1838,19 @@
           <t>SPIP</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>35</v>
+      </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
@@ -1692,6 +1913,19 @@
           <t>IND</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>47</v>
+      </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
@@ -1753,6 +1987,19 @@
         <is>
           <t>IND</t>
         </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>MALE</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>53</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
